--- a/shifts.xlsx.xlsx
+++ b/shifts.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CityTech\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3832BDAE-5D5F-48B6-A887-41602BEA2564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49CAC1F-E36B-4B88-83D6-7FA749287028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>التاريخ</t>
   </si>
@@ -45,13 +45,61 @@
     <t>أولى</t>
   </si>
   <si>
-    <t>المهدي,شلار</t>
-  </si>
-  <si>
-    <t>علي,غياث</t>
-  </si>
-  <si>
-    <t>ثانية</t>
+    <t>عمر شيخ أمين</t>
+  </si>
+  <si>
+    <t>أحمد حفار</t>
+  </si>
+  <si>
+    <t>عناية</t>
+  </si>
+  <si>
+    <t>ريان الأفندي</t>
+  </si>
+  <si>
+    <t>شاكر دباغ</t>
+  </si>
+  <si>
+    <t>جناح</t>
+  </si>
+  <si>
+    <t>غياث دحدوح</t>
+  </si>
+  <si>
+    <t>أمير الراشد</t>
+  </si>
+  <si>
+    <t>بارد</t>
+  </si>
+  <si>
+    <t>محمد طنب</t>
+  </si>
+  <si>
+    <t>مصطفى الشب</t>
+  </si>
+  <si>
+    <t>اب بكر</t>
+  </si>
+  <si>
+    <t>وفائي</t>
+  </si>
+  <si>
+    <t>فاطمة كادك</t>
+  </si>
+  <si>
+    <t>محمد إبراهيم</t>
+  </si>
+  <si>
+    <t>كلارجي</t>
+  </si>
+  <si>
+    <t>قصاب</t>
+  </si>
+  <si>
+    <t>دهان</t>
+  </si>
+  <si>
+    <t>قسوم</t>
   </si>
 </sst>
 </file>
@@ -87,10 +135,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -371,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -384,7 +431,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -399,7 +446,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -410,10 +457,206 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
